--- a/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
+++ b/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nisharg.S\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NishargSoni-458\RKIT_TRAINING\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{175E821C-FEC0-4227-B6C6-37F14249FC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E88DE8-154C-496D-9387-6DD9E2850723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dot Net Core" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -78,9 +67,6 @@
     <t>Pipeline order, built-in middleware, writing custom middleware</t>
   </si>
   <si>
-    <t>Dependency Injection</t>
-  </si>
-  <si>
     <t>Service lifetimes (Transient/Scoped/Singleton), options pattern</t>
   </si>
   <si>
@@ -244,6 +230,24 @@
   </si>
   <si>
     <t>pg_dump/pg_restore, pg_basebackup; PITR basics</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Study of .NET Core</t>
+  </si>
+  <si>
+    <t>Made Demos For DI,Options,Routing</t>
+  </si>
+  <si>
+    <t>Made InventoryMgt Demo using all learned .NET Core Concepts</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Domm</t>
   </si>
 </sst>
 </file>
@@ -315,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -324,6 +328,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715BBE0F-888C-4169-8ED5-7B1E0A5D1E26}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
@@ -707,10 +720,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -725,10 +738,10 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -737,16 +750,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -755,16 +768,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -773,16 +786,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -791,16 +804,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>29</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -809,16 +822,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -827,10 +840,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
         <v>34</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -839,6 +852,67 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C16" s="5">
+        <v>46035</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="7">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C20" s="7"/>
+      <c r="D20" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7">
+        <f>SUM(F16:F20)</f>
+        <v>9.25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -882,16 +956,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -899,16 +973,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
         <v>40</v>
       </c>
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -916,16 +990,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
         <v>42</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>43</v>
       </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -933,16 +1007,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
-        <v>46</v>
-      </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -950,16 +1024,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
         <v>47</v>
       </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -967,16 +1041,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
         <v>49</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>50</v>
       </c>
-      <c r="D7" t="s">
-        <v>51</v>
-      </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -984,16 +1058,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1001,16 +1075,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
         <v>54</v>
       </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1018,16 +1092,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>57</v>
-      </c>
-      <c r="E10" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1035,16 +1109,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
         <v>59</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>60</v>
       </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1052,16 +1126,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
         <v>62</v>
       </c>
-      <c r="D12" t="s">
-        <v>63</v>
-      </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1069,16 +1143,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
         <v>64</v>
       </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1086,16 +1160,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
         <v>66</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>67</v>
       </c>
-      <c r="D14" t="s">
-        <v>68</v>
-      </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
+++ b/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NishargSoni-458\RKIT_TRAINING\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E88DE8-154C-496D-9387-6DD9E2850723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD992D9-DA2D-4A30-B264-537D8679619C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
   <si>
     <t>#</t>
   </si>
@@ -230,24 +230,6 @@
   </si>
   <si>
     <t>pg_dump/pg_restore, pg_basebackup; PITR basics</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Study of .NET Core</t>
-  </si>
-  <si>
-    <t>Made Demos For DI,Options,Routing</t>
-  </si>
-  <si>
-    <t>Made InventoryMgt Demo using all learned .NET Core Concepts</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Domm</t>
   </si>
 </sst>
 </file>
@@ -326,9 +308,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -337,6 +316,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,7 +669,7 @@
       <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -707,7 +689,7 @@
       <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -725,7 +707,7 @@
       <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -743,7 +725,7 @@
       <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -761,7 +743,7 @@
       <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -779,7 +761,7 @@
       <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -797,7 +779,7 @@
       <c r="E9" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -815,7 +797,7 @@
       <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -833,7 +815,7 @@
       <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -845,7 +827,7 @@
       <c r="E12" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E14" s="3"/>
@@ -854,65 +836,40 @@
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C16" s="5">
-        <v>46035</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="7">
-        <v>4</v>
-      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="7">
-        <v>3.5</v>
-      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F19" s="7">
-        <v>1.5</v>
-      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C20" s="7"/>
-      <c r="D20" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="7">
-        <v>0.25</v>
-      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7">
-        <f>SUM(F16:F20)</f>
-        <v>9.25</v>
-      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1178,9 +1135,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1322,19 +1282,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA6786B-8A42-4A0D-80B4-9DE5209F0E64}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B1235E-D1DD-4EED-93B5-5B38ADCC7F24}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1358,9 +1314,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B1235E-D1DD-4EED-93B5-5B38ADCC7F24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA6786B-8A42-4A0D-80B4-9DE5209F0E64}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
+++ b/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NishargSoni-458\RKIT_TRAINING\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD992D9-DA2D-4A30-B264-537D8679619C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5558B68-DFFC-463F-8063-4B7B14742B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1135,15 +1135,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F3C32926E4737E47B27DDAA5D371959A" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="10250be6089a57ac4e60aefa3d8c7247">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7998c3e-7f65-4586-b9f5-db7168bdbc10" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f71cd174da29f72f20168de9339b0a7a" ns2:_="">
     <xsd:import namespace="a7998c3e-7f65-4586-b9f5-db7168bdbc10"/>
@@ -1281,21 +1272,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B1235E-D1DD-4EED-93B5-5B38ADCC7F24}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD60CB27-9450-479F-9CDA-C8096A56D103}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1313,11 +1305,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA6786B-8A42-4A0D-80B4-9DE5209F0E64}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B1235E-D1DD-4EED-93B5-5B38ADCC7F24}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
+++ b/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NishargSoni-458\RKIT_TRAINING\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5558B68-DFFC-463F-8063-4B7B14742B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B22A4E-9EDF-4B53-96F0-7DF414346E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1273,18 +1273,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1306,18 +1306,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B1235E-D1DD-4EED-93B5-5B38ADCC7F24}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA6786B-8A42-4A0D-80B4-9DE5209F0E64}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B1235E-D1DD-4EED-93B5-5B38ADCC7F24}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
+++ b/Docs/Nisharg_Post_Joining_Sheet_G2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NishargSoni-458\RKIT_TRAINING\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B22A4E-9EDF-4B53-96F0-7DF414346E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B10B28-DA04-4732-B7C5-EA822C474B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dot Net Core" sheetId="3" r:id="rId1"/>
@@ -1273,18 +1273,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1306,18 +1306,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B1235E-D1DD-4EED-93B5-5B38ADCC7F24}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA6786B-8A42-4A0D-80B4-9DE5209F0E64}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43B1235E-D1DD-4EED-93B5-5B38ADCC7F24}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>